--- a/data/trans_orig/P1413-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P1413-Edad-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de dolor de espalda en 2007</t>
+          <t>Población con diagnóstico de dolor de espalda, cuello, hombro, cintura (cervical/lumbar) en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>12040</t>
+          <t>12487</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>30490</t>
+          <t>29806</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>15151</t>
+          <t>14993</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>32639</t>
+          <t>32200</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>6,89%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>29376</t>
+          <t>30947</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>54622</t>
+          <t>55722</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,79%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>463574</t>
+          <t>464258</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>482024</t>
+          <t>481577</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,83%</t>
+          <t>93,97%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,56%</t>
+          <t>97,47%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>434850</t>
+          <t>435289</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>452338</t>
+          <t>452496</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,02%</t>
+          <t>93,11%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,76%</t>
+          <t>96,79%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>906931</t>
+          <t>905831</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>932177</t>
+          <t>930606</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,32%</t>
+          <t>94,21%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,94%</t>
+          <t>96,78%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>40180</t>
+          <t>39110</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>68176</t>
+          <t>68343</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>9,29%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>45611</t>
+          <t>46602</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>76185</t>
+          <t>76825</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>12,18%</t>
+          <t>12,28%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>93245</t>
+          <t>94093</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>132979</t>
+          <t>137028</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>6,91%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,77%</t>
+          <t>10,07%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>667313</t>
+          <t>667146</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>695309</t>
+          <t>696379</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>90,73%</t>
+          <t>90,71%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>94,54%</t>
+          <t>94,68%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>549309</t>
+          <t>548669</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>579883</t>
+          <t>578892</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>87,82%</t>
+          <t>87,72%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>92,71%</t>
+          <t>92,55%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1228003</t>
+          <t>1223954</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1267737</t>
+          <t>1266889</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>90,23%</t>
+          <t>89,93%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>93,15%</t>
+          <t>93,09%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>75625</t>
+          <t>75441</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>110350</t>
+          <t>109393</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>11,84%</t>
+          <t>11,81%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>17,28%</t>
+          <t>17,13%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>78843</t>
+          <t>79713</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>115592</t>
+          <t>116643</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>11,43%</t>
+          <t>11,56%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>16,76%</t>
+          <t>16,91%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>163196</t>
+          <t>165646</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>216399</t>
+          <t>214435</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>12,29%</t>
+          <t>12,47%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>16,29%</t>
+          <t>16,14%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>528318</t>
+          <t>529275</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>563043</t>
+          <t>563227</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>82,72%</t>
+          <t>82,87%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>88,16%</t>
+          <t>88,19%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>574152</t>
+          <t>573101</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>610901</t>
+          <t>610031</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>83,24%</t>
+          <t>83,09%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>88,57%</t>
+          <t>88,44%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1112013</t>
+          <t>1113977</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1165216</t>
+          <t>1162766</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>83,71%</t>
+          <t>83,86%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>87,71%</t>
+          <t>87,53%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>82615</t>
+          <t>84440</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>118876</t>
+          <t>119560</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>15,91%</t>
+          <t>16,27%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>22,9%</t>
+          <t>23,03%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>100624</t>
+          <t>101364</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>137635</t>
+          <t>138697</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>19,51%</t>
+          <t>19,66%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>26,69%</t>
+          <t>26,9%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>191101</t>
+          <t>192011</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>246031</t>
+          <t>243058</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>18,47%</t>
+          <t>18,56%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>23,78%</t>
+          <t>23,49%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>400271</t>
+          <t>399587</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>436532</t>
+          <t>434707</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>77,1%</t>
+          <t>76,97%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>84,09%</t>
+          <t>83,73%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>378007</t>
+          <t>376945</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>415018</t>
+          <t>414278</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>73,31%</t>
+          <t>73,1%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>80,49%</t>
+          <t>80,34%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>788758</t>
+          <t>791731</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>843688</t>
+          <t>842778</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>76,22%</t>
+          <t>76,51%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>81,53%</t>
+          <t>81,44%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>98934</t>
+          <t>99470</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>136719</t>
+          <t>133783</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>25,58%</t>
+          <t>25,72%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>35,35%</t>
+          <t>34,6%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>88156</t>
+          <t>88855</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>122934</t>
+          <t>125236</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>21,82%</t>
+          <t>21,99%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>30,43%</t>
+          <t>31,0%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>200044</t>
+          <t>200704</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>248036</t>
+          <t>249754</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>25,3%</t>
+          <t>25,38%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>31,37%</t>
+          <t>31,59%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>249991</t>
+          <t>252927</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>287776</t>
+          <t>287240</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>64,65%</t>
+          <t>65,4%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>74,42%</t>
+          <t>74,28%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>281052</t>
+          <t>278750</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>315830</t>
+          <t>315131</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>69,57%</t>
+          <t>69,0%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>78,18%</t>
+          <t>78,01%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>542660</t>
+          <t>540942</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>590652</t>
+          <t>589992</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>68,63%</t>
+          <t>68,41%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>74,7%</t>
+          <t>74,62%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>63800</t>
+          <t>62477</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>92247</t>
+          <t>92807</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>21,81%</t>
+          <t>21,35%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>31,53%</t>
+          <t>31,72%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>111772</t>
+          <t>110933</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>145364</t>
+          <t>144883</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>32,59%</t>
+          <t>32,35%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>42,39%</t>
+          <t>42,25%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>182268</t>
+          <t>181903</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>225689</t>
+          <t>227615</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>28,68%</t>
+          <t>28,62%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>35,51%</t>
+          <t>35,82%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>200336</t>
+          <t>199776</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>228783</t>
+          <t>230106</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>68,47%</t>
+          <t>68,28%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>78,19%</t>
+          <t>78,65%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>197570</t>
+          <t>198051</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>231162</t>
+          <t>232001</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>57,61%</t>
+          <t>57,75%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>67,41%</t>
+          <t>67,65%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>409828</t>
+          <t>407902</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>453249</t>
+          <t>453614</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>64,49%</t>
+          <t>64,18%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>71,32%</t>
+          <t>71,38%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>59284</t>
+          <t>60218</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>86790</t>
+          <t>86327</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>28,25%</t>
+          <t>28,69%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>41,35%</t>
+          <t>41,13%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>101654</t>
+          <t>102486</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>138194</t>
+          <t>138369</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>30,44%</t>
+          <t>30,69%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>41,39%</t>
+          <t>41,44%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>170173</t>
+          <t>169062</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>215387</t>
+          <t>213774</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>31,29%</t>
+          <t>31,09%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>39,61%</t>
+          <t>39,31%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>123093</t>
+          <t>123556</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>150599</t>
+          <t>149665</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>58,65%</t>
+          <t>58,87%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>71,75%</t>
+          <t>71,31%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>195714</t>
+          <t>195539</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>232254</t>
+          <t>231422</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>58,61%</t>
+          <t>58,56%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>69,56%</t>
+          <t>69,31%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>328404</t>
+          <t>330017</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>373618</t>
+          <t>374729</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>60,39%</t>
+          <t>60,69%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>68,71%</t>
+          <t>68,91%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>485131</t>
+          <t>491205</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>571871</t>
+          <t>571470</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>14,81%</t>
+          <t>14,99%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>17,45%</t>
+          <t>17,44%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>604265</t>
+          <t>602194</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>696767</t>
+          <t>692257</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>17,88%</t>
+          <t>17,82%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>20,62%</t>
+          <t>20,49%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1109635</t>
+          <t>1123590</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1242998</t>
+          <t>1242838</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>16,67%</t>
+          <t>16,88%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>18,68%</t>
+          <t>18,67%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2704672</t>
+          <t>2705073</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2791412</t>
+          <t>2785338</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>82,55%</t>
+          <t>82,56%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>85,19%</t>
+          <t>85,01%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2682430</t>
+          <t>2686940</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2774932</t>
+          <t>2777003</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>79,38%</t>
+          <t>79,51%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>82,12%</t>
+          <t>82,18%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>5412743</t>
+          <t>5412903</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>5546106</t>
+          <t>5532151</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>81,32%</t>
+          <t>81,33%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>83,33%</t>
+          <t>83,12%</t>
         </is>
       </c>
     </row>
@@ -3517,7 +3517,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de dolor de espalda en 2012</t>
+          <t>Población con diagnóstico de dolor de espalda, cuello, hombro, cintura (cervical/lumbar) en 2012 (tasa de respuesta: 99,97%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3712,12 +3712,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5429</t>
+          <t>5818</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>20948</t>
+          <t>21016</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3747,12 +3747,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>9795</t>
+          <t>9854</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>26601</t>
+          <t>27230</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3762,12 +3762,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>6,33%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3782,12 +3782,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>19818</t>
+          <t>18367</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>40429</t>
+          <t>40123</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3797,12 +3797,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,54%</t>
         </is>
       </c>
     </row>
@@ -3825,12 +3825,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>433198</t>
+          <t>433130</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>448717</t>
+          <t>448328</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3840,12 +3840,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,39%</t>
+          <t>95,37%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,8%</t>
+          <t>98,72%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3860,12 +3860,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>403629</t>
+          <t>403000</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>420435</t>
+          <t>420376</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3875,12 +3875,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,82%</t>
+          <t>93,67%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,72%</t>
+          <t>97,71%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>843947</t>
+          <t>844253</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>864558</t>
+          <t>866009</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3910,12 +3910,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,43%</t>
+          <t>95,46%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,76%</t>
+          <t>97,92%</t>
         </is>
       </c>
     </row>
@@ -4055,12 +4055,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>21825</t>
+          <t>22019</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>46428</t>
+          <t>46468</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4070,7 +4070,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -4090,12 +4090,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>36199</t>
+          <t>37073</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>64331</t>
+          <t>64797</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,54%</t>
+          <t>10,62%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4125,12 +4125,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>64867</t>
+          <t>64158</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>100971</t>
+          <t>101687</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4140,12 +4140,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,78%</t>
+          <t>7,84%</t>
         </is>
       </c>
     </row>
@@ -4168,12 +4168,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>640659</t>
+          <t>640619</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>665262</t>
+          <t>665068</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4188,7 +4188,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,82%</t>
+          <t>96,8%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>545924</t>
+          <t>545458</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>574056</t>
+          <t>573182</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>89,46%</t>
+          <t>89,38%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,07%</t>
+          <t>93,93%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4238,12 +4238,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1196371</t>
+          <t>1195655</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1232475</t>
+          <t>1233184</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4253,12 +4253,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,22%</t>
+          <t>92,16%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,0%</t>
+          <t>95,05%</t>
         </is>
       </c>
     </row>
@@ -4398,12 +4398,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>31175</t>
+          <t>30861</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>55681</t>
+          <t>55814</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>8,19%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>75239</t>
+          <t>75682</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>112054</t>
+          <t>113938</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10,6%</t>
+          <t>10,67%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>15,79%</t>
+          <t>16,06%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>114350</t>
+          <t>113845</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>158854</t>
+          <t>158112</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4483,12 +4483,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>8,18%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>11,42%</t>
+          <t>11,36%</t>
         </is>
       </c>
     </row>
@@ -4511,12 +4511,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>626182</t>
+          <t>626049</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>650688</t>
+          <t>651002</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>91,83%</t>
+          <t>91,81%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>95,43%</t>
+          <t>95,47%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4546,12 +4546,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>597520</t>
+          <t>595636</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>634335</t>
+          <t>633892</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>84,21%</t>
+          <t>83,94%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>89,4%</t>
+          <t>89,33%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4581,12 +4581,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1232583</t>
+          <t>1233325</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1277087</t>
+          <t>1277592</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>88,58%</t>
+          <t>88,64%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>91,78%</t>
+          <t>91,82%</t>
         </is>
       </c>
     </row>
@@ -4741,12 +4741,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>40577</t>
+          <t>42655</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>69900</t>
+          <t>74981</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4756,12 +4756,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>6,94%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,37%</t>
+          <t>12,2%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>88414</t>
+          <t>88827</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>129531</t>
+          <t>129838</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4791,12 +4791,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14,39%</t>
+          <t>14,46%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>21,09%</t>
+          <t>21,14%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>137799</t>
+          <t>139543</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>188161</t>
+          <t>192361</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4826,12 +4826,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>11,21%</t>
+          <t>11,36%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>15,31%</t>
+          <t>15,65%</t>
         </is>
       </c>
     </row>
@@ -4854,12 +4854,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>544717</t>
+          <t>539636</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>574040</t>
+          <t>571962</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4869,12 +4869,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>88,63%</t>
+          <t>87,8%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>93,4%</t>
+          <t>93,06%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>484733</t>
+          <t>484426</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>525850</t>
+          <t>525437</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4904,12 +4904,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>78,91%</t>
+          <t>78,86%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>85,61%</t>
+          <t>85,54%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1040719</t>
+          <t>1036519</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1091081</t>
+          <t>1089337</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4939,12 +4939,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>84,69%</t>
+          <t>84,35%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>88,79%</t>
+          <t>88,64%</t>
         </is>
       </c>
     </row>
@@ -5084,12 +5084,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>40997</t>
+          <t>39651</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>69566</t>
+          <t>69158</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5099,12 +5099,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>9,55%</t>
+          <t>9,23%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>16,2%</t>
+          <t>16,1%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>98987</t>
+          <t>97546</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>138662</t>
+          <t>138048</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5134,12 +5134,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>22,11%</t>
+          <t>21,78%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>30,97%</t>
+          <t>30,83%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>147605</t>
+          <t>148604</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>196829</t>
+          <t>195977</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5169,12 +5169,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>16,83%</t>
+          <t>16,94%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>22,44%</t>
+          <t>22,34%</t>
         </is>
       </c>
     </row>
@@ -5197,12 +5197,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>359863</t>
+          <t>360271</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>388432</t>
+          <t>389778</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5212,12 +5212,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>83,8%</t>
+          <t>83,9%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>90,45%</t>
+          <t>90,77%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>309138</t>
+          <t>309752</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>348813</t>
+          <t>350254</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5247,12 +5247,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>69,03%</t>
+          <t>69,17%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>77,89%</t>
+          <t>78,22%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>680400</t>
+          <t>681252</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>729624</t>
+          <t>728625</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5282,12 +5282,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>77,56%</t>
+          <t>77,66%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>83,17%</t>
+          <t>83,06%</t>
         </is>
       </c>
     </row>
@@ -5427,12 +5427,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>44800</t>
+          <t>44242</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>74339</t>
+          <t>73884</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5442,12 +5442,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>14,46%</t>
+          <t>14,28%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>24,0%</t>
+          <t>23,85%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>91690</t>
+          <t>95099</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>127134</t>
+          <t>128176</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5477,12 +5477,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>25,9%</t>
+          <t>26,86%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>35,91%</t>
+          <t>36,21%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>145100</t>
+          <t>148106</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>190945</t>
+          <t>193199</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>21,86%</t>
+          <t>22,31%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>28,77%</t>
+          <t>29,11%</t>
         </is>
       </c>
     </row>
@@ -5540,12 +5540,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>235447</t>
+          <t>235902</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>264986</t>
+          <t>265544</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5555,12 +5555,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>76,0%</t>
+          <t>76,15%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>85,54%</t>
+          <t>85,72%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>226862</t>
+          <t>225820</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>262306</t>
+          <t>258897</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5590,12 +5590,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>64,09%</t>
+          <t>63,79%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>74,1%</t>
+          <t>73,14%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>472837</t>
+          <t>470583</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>518682</t>
+          <t>515676</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5625,12 +5625,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>71,23%</t>
+          <t>70,89%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>78,14%</t>
+          <t>77,69%</t>
         </is>
       </c>
     </row>
@@ -5770,12 +5770,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>42392</t>
+          <t>42015</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>69297</t>
+          <t>70535</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5785,12 +5785,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>16,97%</t>
+          <t>16,82%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>27,74%</t>
+          <t>28,23%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>131852</t>
+          <t>132346</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>170117</t>
+          <t>173496</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5820,12 +5820,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>33,9%</t>
+          <t>34,02%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>43,73%</t>
+          <t>44,6%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>181475</t>
+          <t>182036</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>230108</t>
+          <t>232446</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5855,12 +5855,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>28,41%</t>
+          <t>28,5%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>36,02%</t>
+          <t>36,39%</t>
         </is>
       </c>
     </row>
@@ -5883,12 +5883,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>180554</t>
+          <t>179316</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>207459</t>
+          <t>207836</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5898,12 +5898,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>72,26%</t>
+          <t>71,77%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>83,03%</t>
+          <t>83,18%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>218862</t>
+          <t>215483</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>257127</t>
+          <t>256633</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5933,12 +5933,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>56,27%</t>
+          <t>55,4%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>66,1%</t>
+          <t>65,98%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>408722</t>
+          <t>406384</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>457355</t>
+          <t>456794</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5968,12 +5968,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>63,98%</t>
+          <t>63,61%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>71,59%</t>
+          <t>71,5%</t>
         </is>
       </c>
     </row>
@@ -6113,12 +6113,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>278211</t>
+          <t>278887</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>345079</t>
+          <t>345582</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>10,08%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>599713</t>
+          <t>602211</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>696141</t>
+          <t>694407</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>16,87%</t>
+          <t>16,94%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>19,58%</t>
+          <t>19,53%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>899865</t>
+          <t>896548</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1016775</t>
+          <t>1013551</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6198,12 +6198,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>12,89%</t>
+          <t>12,84%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>14,56%</t>
+          <t>14,52%</t>
         </is>
       </c>
     </row>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3081700</t>
+          <t>3081197</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3148568</t>
+          <t>3147892</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>89,93%</t>
+          <t>89,92%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>91,88%</t>
+          <t>91,86%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2858957</t>
+          <t>2860691</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2955385</t>
+          <t>2952887</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>80,42%</t>
+          <t>80,47%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>83,13%</t>
+          <t>83,06%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>5965102</t>
+          <t>5968326</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6082012</t>
+          <t>6085329</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6311,12 +6311,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>85,44%</t>
+          <t>85,48%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>87,11%</t>
+          <t>87,16%</t>
         </is>
       </c>
     </row>
@@ -6496,7 +6496,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de dolor de espalda en 2016</t>
+          <t>Población con diagnóstico de dolor de espalda, cuello, hombro, cintura (cervical/lumbar) en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6696,7 +6696,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7726</t>
+          <t>7724</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6726,12 +6726,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>5713</t>
+          <t>5629</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>17704</t>
+          <t>18229</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6741,12 +6741,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6761,12 +6761,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>7319</t>
+          <t>7686</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>21598</t>
+          <t>21826</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,68%</t>
         </is>
       </c>
     </row>
@@ -6804,7 +6804,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>411737</t>
+          <t>411739</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -6839,12 +6839,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>378051</t>
+          <t>377526</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>390042</t>
+          <t>390126</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6854,12 +6854,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,53%</t>
+          <t>95,39%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,56%</t>
+          <t>98,58%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6874,12 +6874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>793620</t>
+          <t>793392</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>807899</t>
+          <t>807532</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6889,12 +6889,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,35%</t>
+          <t>97,32%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,1%</t>
+          <t>99,06%</t>
         </is>
       </c>
     </row>
@@ -7034,12 +7034,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9713</t>
+          <t>9435</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>28346</t>
+          <t>27962</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7049,12 +7049,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7069,12 +7069,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>22055</t>
+          <t>22130</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>43991</t>
+          <t>44233</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7084,12 +7084,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>7,85%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7104,12 +7104,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>34652</t>
+          <t>36234</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>62893</t>
+          <t>64279</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7119,12 +7119,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,57%</t>
         </is>
       </c>
     </row>
@@ -7147,12 +7147,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>562150</t>
+          <t>562534</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>580783</t>
+          <t>581061</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7162,12 +7162,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,2%</t>
+          <t>95,26%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,36%</t>
+          <t>98,4%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7182,12 +7182,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>519553</t>
+          <t>519311</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>541489</t>
+          <t>541414</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7197,12 +7197,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,19%</t>
+          <t>92,15%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,09%</t>
+          <t>96,07%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7217,12 +7217,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1091147</t>
+          <t>1089761</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1119388</t>
+          <t>1117806</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7232,12 +7232,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,55%</t>
+          <t>94,43%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,0%</t>
+          <t>96,86%</t>
         </is>
       </c>
     </row>
@@ -7377,12 +7377,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>33092</t>
+          <t>34340</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>60532</t>
+          <t>61125</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7392,12 +7392,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>9,05%</t>
+          <t>9,14%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7412,12 +7412,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>45135</t>
+          <t>44306</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>73019</t>
+          <t>72945</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7427,12 +7427,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>11,04%</t>
+          <t>11,03%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7447,12 +7447,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>83454</t>
+          <t>84981</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>124088</t>
+          <t>125592</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7462,12 +7462,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>9,44%</t>
         </is>
       </c>
     </row>
@@ -7490,12 +7490,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>608565</t>
+          <t>607972</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>636005</t>
+          <t>634757</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7505,12 +7505,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>90,95%</t>
+          <t>90,86%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>95,05%</t>
+          <t>94,87%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7525,12 +7525,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>588367</t>
+          <t>588441</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>616251</t>
+          <t>617080</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7540,12 +7540,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>88,96%</t>
+          <t>88,97%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>93,18%</t>
+          <t>93,3%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7560,12 +7560,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1206395</t>
+          <t>1204891</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1247029</t>
+          <t>1245502</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7575,12 +7575,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>90,67%</t>
+          <t>90,56%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>93,73%</t>
+          <t>93,61%</t>
         </is>
       </c>
     </row>
@@ -7720,12 +7720,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>45538</t>
+          <t>46545</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>76758</t>
+          <t>76556</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7735,12 +7735,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,88%</t>
+          <t>11,85%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7755,12 +7755,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>69297</t>
+          <t>71011</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>106357</t>
+          <t>105199</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7770,12 +7770,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,68%</t>
+          <t>10,94%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>16,39%</t>
+          <t>16,21%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7790,12 +7790,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>125464</t>
+          <t>124050</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>170759</t>
+          <t>169840</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7805,12 +7805,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>9,58%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>13,18%</t>
+          <t>13,11%</t>
         </is>
       </c>
     </row>
@@ -7833,12 +7833,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>569290</t>
+          <t>569492</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>600510</t>
+          <t>599503</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>88,12%</t>
+          <t>88,15%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>92,95%</t>
+          <t>92,8%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7868,12 +7868,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>542720</t>
+          <t>543878</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>579780</t>
+          <t>578066</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7883,12 +7883,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>83,61%</t>
+          <t>83,79%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>89,32%</t>
+          <t>89,06%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7903,12 +7903,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1124366</t>
+          <t>1125285</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1169661</t>
+          <t>1171075</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7918,12 +7918,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>86,82%</t>
+          <t>86,89%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>90,31%</t>
+          <t>90,42%</t>
         </is>
       </c>
     </row>
@@ -8063,12 +8063,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>45560</t>
+          <t>46421</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>77175</t>
+          <t>76942</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8078,12 +8078,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>9,53%</t>
+          <t>9,71%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>16,15%</t>
+          <t>16,1%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8098,12 +8098,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>85901</t>
+          <t>86303</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>124026</t>
+          <t>123113</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8113,12 +8113,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>17,29%</t>
+          <t>17,37%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>24,96%</t>
+          <t>24,78%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>139176</t>
+          <t>141894</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>189989</t>
+          <t>192205</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8148,12 +8148,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>14,28%</t>
+          <t>14,56%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>19,49%</t>
+          <t>19,72%</t>
         </is>
       </c>
     </row>
@@ -8176,12 +8176,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>400743</t>
+          <t>400976</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>432358</t>
+          <t>431497</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8191,12 +8191,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>83,85%</t>
+          <t>83,9%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>90,47%</t>
+          <t>90,29%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8211,12 +8211,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>372823</t>
+          <t>373736</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>410948</t>
+          <t>410546</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8226,12 +8226,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>75,04%</t>
+          <t>75,22%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>82,71%</t>
+          <t>82,63%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8246,12 +8246,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>784778</t>
+          <t>782562</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>835591</t>
+          <t>832873</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8261,12 +8261,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>80,51%</t>
+          <t>80,28%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>85,72%</t>
+          <t>85,44%</t>
         </is>
       </c>
     </row>
@@ -8406,12 +8406,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>32996</t>
+          <t>32311</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>59359</t>
+          <t>56743</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8421,12 +8421,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>9,87%</t>
+          <t>9,66%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>17,75%</t>
+          <t>16,97%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8441,12 +8441,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>65394</t>
+          <t>65841</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>95868</t>
+          <t>98978</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8456,12 +8456,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>17,31%</t>
+          <t>17,43%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>25,38%</t>
+          <t>26,2%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8476,12 +8476,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>104121</t>
+          <t>105700</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>145536</t>
+          <t>147990</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8491,12 +8491,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>14,62%</t>
+          <t>14,84%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>20,44%</t>
+          <t>20,78%</t>
         </is>
       </c>
     </row>
@@ -8519,12 +8519,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>274971</t>
+          <t>277587</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>301334</t>
+          <t>302019</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8534,12 +8534,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>82,25%</t>
+          <t>83,03%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>90,13%</t>
+          <t>90,34%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8554,12 +8554,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>281894</t>
+          <t>278784</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>312368</t>
+          <t>311921</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8569,12 +8569,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>74,62%</t>
+          <t>73,8%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>82,69%</t>
+          <t>82,57%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8589,12 +8589,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>566556</t>
+          <t>564102</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>607971</t>
+          <t>606392</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8604,12 +8604,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>79,56%</t>
+          <t>79,22%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>85,38%</t>
+          <t>85,16%</t>
         </is>
       </c>
     </row>
@@ -8749,12 +8749,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>39186</t>
+          <t>39496</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>63592</t>
+          <t>62595</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8764,12 +8764,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>15,25%</t>
+          <t>15,37%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>24,74%</t>
+          <t>24,36%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8784,12 +8784,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>103858</t>
+          <t>102844</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>144333</t>
+          <t>143087</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8799,12 +8799,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>25,95%</t>
+          <t>25,7%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>36,07%</t>
+          <t>35,76%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8819,12 +8819,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>147560</t>
+          <t>146480</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>197044</t>
+          <t>197249</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8834,12 +8834,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>22,45%</t>
+          <t>22,29%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>29,98%</t>
+          <t>30,02%</t>
         </is>
       </c>
     </row>
@@ -8862,12 +8862,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>193406</t>
+          <t>194403</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>217812</t>
+          <t>217502</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8877,12 +8877,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>75,26%</t>
+          <t>75,64%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>84,75%</t>
+          <t>84,63%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8897,12 +8897,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>255836</t>
+          <t>257082</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>296311</t>
+          <t>297325</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8912,12 +8912,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>63,93%</t>
+          <t>64,24%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>74,05%</t>
+          <t>74,3%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8932,12 +8932,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>460123</t>
+          <t>459918</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>509607</t>
+          <t>510687</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8947,12 +8947,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>70,02%</t>
+          <t>69,98%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>77,55%</t>
+          <t>77,71%</t>
         </is>
       </c>
     </row>
@@ -9092,12 +9092,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>245425</t>
+          <t>246051</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>315170</t>
+          <t>310896</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9107,12 +9107,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>7,25%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>9,16%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9127,12 +9127,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>444603</t>
+          <t>453078</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>535404</t>
+          <t>541806</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9142,12 +9142,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>12,54%</t>
+          <t>12,78%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>15,11%</t>
+          <t>15,29%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9162,12 +9162,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>715865</t>
+          <t>716938</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>826964</t>
+          <t>823410</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9177,12 +9177,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>10,32%</t>
+          <t>10,33%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>11,92%</t>
+          <t>11,87%</t>
         </is>
       </c>
     </row>
@@ -9205,12 +9205,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3079180</t>
+          <t>3083454</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3148925</t>
+          <t>3148299</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>90,71%</t>
+          <t>90,84%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>92,77%</t>
+          <t>92,75%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9240,12 +9240,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3009138</t>
+          <t>3002736</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3099939</t>
+          <t>3091464</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9255,12 +9255,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>84,89%</t>
+          <t>84,71%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>87,46%</t>
+          <t>87,22%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9275,12 +9275,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6111928</t>
+          <t>6115482</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6223027</t>
+          <t>6221954</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9290,12 +9290,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>88,08%</t>
+          <t>88,13%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>89,68%</t>
+          <t>89,67%</t>
         </is>
       </c>
     </row>
@@ -9475,7 +9475,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de dolor de espalda en 2023</t>
+          <t>Población con diagnóstico de dolor de espalda, cuello, hombro, cintura (cervical/lumbar) en 2023 (tasa de respuesta: 99,91%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9670,12 +9670,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6501</t>
+          <t>5610</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>42924</t>
+          <t>43169</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -9685,12 +9685,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>10,73%</t>
+          <t>10,79%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9705,12 +9705,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>17466</t>
+          <t>18933</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>48679</t>
+          <t>51760</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -9720,12 +9720,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>6,04%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>15,54%</t>
+          <t>16,53%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9740,12 +9740,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>31006</t>
+          <t>32060</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>74339</t>
+          <t>75007</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -9755,12 +9755,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,42%</t>
+          <t>10,52%</t>
         </is>
       </c>
     </row>
@@ -9783,12 +9783,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>357063</t>
+          <t>356818</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>393486</t>
+          <t>394377</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -9798,12 +9798,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>89,27%</t>
+          <t>89,21%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,37%</t>
+          <t>98,6%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9818,12 +9818,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>264521</t>
+          <t>261440</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>295734</t>
+          <t>294267</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -9833,12 +9833,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>84,46%</t>
+          <t>83,47%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,42%</t>
+          <t>93,96%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9853,12 +9853,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>638848</t>
+          <t>638180</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>682181</t>
+          <t>681127</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -9868,12 +9868,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>89,58%</t>
+          <t>89,48%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,65%</t>
+          <t>95,5%</t>
         </is>
       </c>
     </row>
@@ -10013,12 +10013,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>18797</t>
+          <t>19479</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>45145</t>
+          <t>46272</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -10028,12 +10028,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,72%</t>
+          <t>10,98%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -10048,12 +10048,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>32564</t>
+          <t>32239</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>69754</t>
+          <t>70984</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -10063,12 +10063,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>13,64%</t>
+          <t>13,88%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10083,12 +10083,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>60810</t>
+          <t>58556</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>104817</t>
+          <t>103404</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -10098,12 +10098,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>11,24%</t>
+          <t>11,09%</t>
         </is>
       </c>
     </row>
@@ -10126,12 +10126,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>376142</t>
+          <t>375015</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>402490</t>
+          <t>401808</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -10141,12 +10141,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>89,28%</t>
+          <t>89,02%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>95,54%</t>
+          <t>95,38%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -10161,12 +10161,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>441750</t>
+          <t>440520</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>478940</t>
+          <t>479265</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -10176,12 +10176,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>86,36%</t>
+          <t>86,12%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>93,63%</t>
+          <t>93,7%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -10196,12 +10196,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>827974</t>
+          <t>829387</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>871981</t>
+          <t>874235</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -10211,12 +10211,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>88,76%</t>
+          <t>88,91%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>93,48%</t>
+          <t>93,72%</t>
         </is>
       </c>
     </row>
@@ -10356,12 +10356,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>43872</t>
+          <t>42524</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>73127</t>
+          <t>72116</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -10371,12 +10371,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>8,19%</t>
+          <t>7,94%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>13,65%</t>
+          <t>13,46%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>99049</t>
+          <t>98031</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>130747</t>
+          <t>128773</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -10406,12 +10406,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>18,28%</t>
+          <t>18,09%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>24,13%</t>
+          <t>23,77%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10426,12 +10426,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>150553</t>
+          <t>148960</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>191331</t>
+          <t>191783</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -10441,12 +10441,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>13,97%</t>
+          <t>13,83%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>17,76%</t>
+          <t>17,8%</t>
         </is>
       </c>
     </row>
@@ -10469,12 +10469,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>462451</t>
+          <t>463462</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>491706</t>
+          <t>493054</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -10484,12 +10484,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>86,35%</t>
+          <t>86,54%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>91,81%</t>
+          <t>92,06%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10504,12 +10504,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>411052</t>
+          <t>413026</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>442750</t>
+          <t>443768</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -10519,12 +10519,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>75,87%</t>
+          <t>76,23%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>81,72%</t>
+          <t>81,91%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10539,12 +10539,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>886046</t>
+          <t>885594</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>926824</t>
+          <t>928417</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -10554,12 +10554,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>82,24%</t>
+          <t>82,2%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>86,03%</t>
+          <t>86,17%</t>
         </is>
       </c>
     </row>
@@ -10699,12 +10699,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>56410</t>
+          <t>55384</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>192833</t>
+          <t>192661</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -10714,12 +10714,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>21,75%</t>
+          <t>21,73%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10734,12 +10734,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>161085</t>
+          <t>164727</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>214554</t>
+          <t>215871</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -10749,12 +10749,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>22,63%</t>
+          <t>23,14%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>30,14%</t>
+          <t>30,33%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10769,12 +10769,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>190555</t>
+          <t>185568</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>397105</t>
+          <t>398713</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -10784,12 +10784,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>11,92%</t>
+          <t>11,61%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>24,84%</t>
+          <t>24,94%</t>
         </is>
       </c>
     </row>
@@ -10812,12 +10812,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>693840</t>
+          <t>694012</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>830263</t>
+          <t>831289</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -10827,12 +10827,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>78,25%</t>
+          <t>78,27%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>93,64%</t>
+          <t>93,75%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10847,12 +10847,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>497299</t>
+          <t>495982</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>550768</t>
+          <t>547126</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -10862,12 +10862,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>69,86%</t>
+          <t>69,67%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>77,37%</t>
+          <t>76,86%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10882,12 +10882,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1201421</t>
+          <t>1199813</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1407971</t>
+          <t>1412958</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -10897,12 +10897,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>75,16%</t>
+          <t>75,06%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>88,08%</t>
+          <t>88,39%</t>
         </is>
       </c>
     </row>
@@ -11042,12 +11042,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>133388</t>
+          <t>136186</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>173776</t>
+          <t>174998</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -11057,12 +11057,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>23,81%</t>
+          <t>24,31%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>31,02%</t>
+          <t>31,24%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11077,12 +11077,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>196259</t>
+          <t>196351</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>231442</t>
+          <t>230938</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -11092,12 +11092,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>36,03%</t>
+          <t>36,05%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>42,49%</t>
+          <t>42,4%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11112,12 +11112,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>338787</t>
+          <t>337951</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>392825</t>
+          <t>391364</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -11127,12 +11127,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>30,66%</t>
+          <t>30,58%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>35,55%</t>
+          <t>35,42%</t>
         </is>
       </c>
     </row>
@@ -11155,12 +11155,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>386461</t>
+          <t>385239</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>426849</t>
+          <t>424051</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -11170,12 +11170,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>68,98%</t>
+          <t>68,76%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>76,19%</t>
+          <t>75,69%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11190,12 +11190,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>313286</t>
+          <t>313790</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>348469</t>
+          <t>348377</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -11205,12 +11205,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>57,51%</t>
+          <t>57,6%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>63,97%</t>
+          <t>63,95%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11225,12 +11225,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>712139</t>
+          <t>713600</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>766177</t>
+          <t>767013</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -11240,12 +11240,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>64,45%</t>
+          <t>64,58%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>69,34%</t>
+          <t>69,42%</t>
         </is>
       </c>
     </row>
@@ -11385,12 +11385,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>86460</t>
+          <t>84823</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>112935</t>
+          <t>112146</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -11400,12 +11400,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>23,53%</t>
+          <t>23,08%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>30,73%</t>
+          <t>30,52%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11420,12 +11420,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>269840</t>
+          <t>269997</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>515397</t>
+          <t>507415</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -11435,12 +11435,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>44,35%</t>
+          <t>44,38%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>84,72%</t>
+          <t>83,41%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11455,12 +11455,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>350161</t>
+          <t>350391</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>739553</t>
+          <t>712604</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -11470,12 +11470,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>35,88%</t>
+          <t>35,91%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>75,79%</t>
+          <t>73,03%</t>
         </is>
       </c>
     </row>
@@ -11498,12 +11498,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>254512</t>
+          <t>255301</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>280987</t>
+          <t>282624</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -11513,12 +11513,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>69,27%</t>
+          <t>69,48%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>76,47%</t>
+          <t>76,92%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11533,12 +11533,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>92971</t>
+          <t>100953</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>338528</t>
+          <t>338371</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -11548,12 +11548,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>15,28%</t>
+          <t>16,59%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>55,65%</t>
+          <t>55,62%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11568,12 +11568,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>236261</t>
+          <t>263210</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>625653</t>
+          <t>625423</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -11583,12 +11583,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>24,21%</t>
+          <t>26,97%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>64,12%</t>
+          <t>64,09%</t>
         </is>
       </c>
     </row>
@@ -11728,12 +11728,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>100679</t>
+          <t>99476</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>125281</t>
+          <t>123916</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -11743,12 +11743,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>35,61%</t>
+          <t>35,18%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>44,31%</t>
+          <t>43,82%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11763,12 +11763,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>227940</t>
+          <t>227957</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>258248</t>
+          <t>257456</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -11783,7 +11783,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>60,65%</t>
+          <t>60,46%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11798,12 +11798,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>333526</t>
+          <t>335094</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>372350</t>
+          <t>373697</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -11813,12 +11813,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>47,07%</t>
+          <t>47,29%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>52,55%</t>
+          <t>52,74%</t>
         </is>
       </c>
     </row>
@@ -11841,12 +11841,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>157478</t>
+          <t>158843</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>182080</t>
+          <t>183283</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -11856,12 +11856,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>55,69%</t>
+          <t>56,18%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>64,39%</t>
+          <t>64,82%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11876,12 +11876,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>167583</t>
+          <t>168375</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>197891</t>
+          <t>197874</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -11891,7 +11891,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>39,35%</t>
+          <t>39,54%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -11911,12 +11911,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>336240</t>
+          <t>334893</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>375064</t>
+          <t>373496</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -11926,12 +11926,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>47,45%</t>
+          <t>47,26%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>52,93%</t>
+          <t>52,71%</t>
         </is>
       </c>
     </row>
@@ -12071,12 +12071,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>477330</t>
+          <t>465913</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>669457</t>
+          <t>668553</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -12086,12 +12086,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>13,82%</t>
+          <t>13,49%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>19,38%</t>
+          <t>19,36%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12106,12 +12106,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1071397</t>
+          <t>1069708</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1691433</t>
+          <t>1662016</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -12121,12 +12121,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>29,29%</t>
+          <t>29,25%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>46,25%</t>
+          <t>45,44%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12141,12 +12141,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1638912</t>
+          <t>1629138</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>2431812</t>
+          <t>2479075</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -12156,12 +12156,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>23,05%</t>
+          <t>22,91%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>34,2%</t>
+          <t>34,86%</t>
         </is>
       </c>
     </row>
@@ -12184,12 +12184,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2784511</t>
+          <t>2785415</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2976638</t>
+          <t>2988055</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -12199,12 +12199,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>80,62%</t>
+          <t>80,64%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>86,18%</t>
+          <t>86,51%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12219,12 +12219,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1965849</t>
+          <t>1995266</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2585885</t>
+          <t>2587574</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -12234,12 +12234,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>53,75%</t>
+          <t>54,56%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>70,71%</t>
+          <t>70,75%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12254,12 +12254,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>4679438</t>
+          <t>4632175</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>5472338</t>
+          <t>5482112</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -12269,12 +12269,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>65,8%</t>
+          <t>65,14%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>76,95%</t>
+          <t>77,09%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P1413-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P1413-Edad-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>12487</t>
+          <t>11947</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>29806</t>
+          <t>29870</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>6,05%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>14993</t>
+          <t>14609</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>32200</t>
+          <t>32179</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>30947</t>
+          <t>30319</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>55722</t>
+          <t>56108</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,84%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>464258</t>
+          <t>464194</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>481577</t>
+          <t>482117</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,97%</t>
+          <t>93,95%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,47%</t>
+          <t>97,58%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>435289</t>
+          <t>435310</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>452496</t>
+          <t>452880</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,11%</t>
+          <t>93,12%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,79%</t>
+          <t>96,88%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>905831</t>
+          <t>905445</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>930606</t>
+          <t>931234</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,21%</t>
+          <t>94,16%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,78%</t>
+          <t>96,85%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>39110</t>
+          <t>39363</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>68343</t>
+          <t>67498</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>9,18%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>46602</t>
+          <t>46668</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>76825</t>
+          <t>77773</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>7,46%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>12,28%</t>
+          <t>12,43%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>94093</t>
+          <t>93135</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>137028</t>
+          <t>136330</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>10,02%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>667146</t>
+          <t>667991</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>696379</t>
+          <t>696126</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>90,71%</t>
+          <t>90,82%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>94,68%</t>
+          <t>94,65%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>548669</t>
+          <t>547721</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>578892</t>
+          <t>578826</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>87,72%</t>
+          <t>87,57%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>92,55%</t>
+          <t>92,54%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1223954</t>
+          <t>1224652</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1266889</t>
+          <t>1267847</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>89,93%</t>
+          <t>89,98%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>93,09%</t>
+          <t>93,16%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>75441</t>
+          <t>74726</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>109393</t>
+          <t>110203</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>11,81%</t>
+          <t>11,7%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>17,13%</t>
+          <t>17,26%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>79713</t>
+          <t>79719</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>116643</t>
+          <t>116527</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>16,91%</t>
+          <t>16,89%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>165646</t>
+          <t>164135</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>214435</t>
+          <t>214332</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>12,47%</t>
+          <t>12,36%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>16,14%</t>
+          <t>16,13%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>529275</t>
+          <t>528465</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>563227</t>
+          <t>563942</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>82,87%</t>
+          <t>82,74%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>88,19%</t>
+          <t>88,3%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>573101</t>
+          <t>573217</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>610031</t>
+          <t>610025</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>83,09%</t>
+          <t>83,11%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1113977</t>
+          <t>1114080</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1162766</t>
+          <t>1164277</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>83,86%</t>
+          <t>83,87%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>87,53%</t>
+          <t>87,64%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>84440</t>
+          <t>83786</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>119560</t>
+          <t>119651</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>16,27%</t>
+          <t>16,14%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>23,03%</t>
+          <t>23,05%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>101364</t>
+          <t>99364</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>138697</t>
+          <t>136494</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>19,66%</t>
+          <t>19,27%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>26,9%</t>
+          <t>26,47%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>192011</t>
+          <t>193722</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>243058</t>
+          <t>245938</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>18,56%</t>
+          <t>18,72%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>23,49%</t>
+          <t>23,77%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>399587</t>
+          <t>399496</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>434707</t>
+          <t>435361</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>76,97%</t>
+          <t>76,95%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>83,73%</t>
+          <t>83,86%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>376945</t>
+          <t>379148</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>414278</t>
+          <t>416278</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>73,1%</t>
+          <t>73,53%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>80,34%</t>
+          <t>80,73%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>791731</t>
+          <t>788851</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>842778</t>
+          <t>841067</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>76,51%</t>
+          <t>76,23%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>81,44%</t>
+          <t>81,28%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>99470</t>
+          <t>100570</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>133783</t>
+          <t>135600</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>25,72%</t>
+          <t>26,01%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>34,6%</t>
+          <t>35,07%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>88855</t>
+          <t>87193</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>125236</t>
+          <t>124974</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>21,99%</t>
+          <t>21,58%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>31,0%</t>
+          <t>30,94%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>200704</t>
+          <t>201366</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>249754</t>
+          <t>251421</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>25,38%</t>
+          <t>25,47%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>31,59%</t>
+          <t>31,8%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>252927</t>
+          <t>251110</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>287240</t>
+          <t>286140</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>65,4%</t>
+          <t>64,93%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>74,28%</t>
+          <t>73,99%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>278750</t>
+          <t>279012</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>315131</t>
+          <t>316793</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>69,0%</t>
+          <t>69,06%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>78,01%</t>
+          <t>78,42%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>540942</t>
+          <t>539275</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>589992</t>
+          <t>589330</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>68,41%</t>
+          <t>68,2%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>74,62%</t>
+          <t>74,53%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>62477</t>
+          <t>63494</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>92807</t>
+          <t>92516</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>21,35%</t>
+          <t>21,7%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>31,72%</t>
+          <t>31,62%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>110933</t>
+          <t>112278</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>144883</t>
+          <t>144162</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>32,35%</t>
+          <t>32,74%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>42,25%</t>
+          <t>42,04%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>181903</t>
+          <t>183577</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>227615</t>
+          <t>227891</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>28,62%</t>
+          <t>28,89%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>35,82%</t>
+          <t>35,86%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>199776</t>
+          <t>200067</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>230106</t>
+          <t>229089</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>68,28%</t>
+          <t>68,38%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>78,65%</t>
+          <t>78,3%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>198051</t>
+          <t>198772</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>232001</t>
+          <t>230656</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>57,75%</t>
+          <t>57,96%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>67,65%</t>
+          <t>67,26%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>407902</t>
+          <t>407626</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>453614</t>
+          <t>451940</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>64,18%</t>
+          <t>64,14%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>71,38%</t>
+          <t>71,11%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>60218</t>
+          <t>60851</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>86327</t>
+          <t>86510</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>28,69%</t>
+          <t>28,99%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>41,13%</t>
+          <t>41,22%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>102486</t>
+          <t>103694</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>138369</t>
+          <t>139517</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>30,69%</t>
+          <t>31,05%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>41,44%</t>
+          <t>41,78%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>169062</t>
+          <t>169393</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>213774</t>
+          <t>214535</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>31,09%</t>
+          <t>31,15%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>39,31%</t>
+          <t>39,45%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>123556</t>
+          <t>123373</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>149665</t>
+          <t>149032</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>58,87%</t>
+          <t>58,78%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>71,31%</t>
+          <t>71,01%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>195539</t>
+          <t>194391</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>231422</t>
+          <t>230214</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>58,56%</t>
+          <t>58,22%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>69,31%</t>
+          <t>68,95%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>330017</t>
+          <t>329256</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>374729</t>
+          <t>374398</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>60,69%</t>
+          <t>60,55%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>68,91%</t>
+          <t>68,85%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>491205</t>
+          <t>491274</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>571470</t>
+          <t>578124</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3154,7 +3154,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>17,44%</t>
+          <t>17,64%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>602194</t>
+          <t>601826</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>692257</t>
+          <t>696772</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>17,82%</t>
+          <t>17,81%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>20,49%</t>
+          <t>20,62%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1123590</t>
+          <t>1116665</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1242838</t>
+          <t>1239970</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>16,88%</t>
+          <t>16,78%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>18,67%</t>
+          <t>18,63%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2705073</t>
+          <t>2698419</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2785338</t>
+          <t>2785269</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,7 +3262,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>82,56%</t>
+          <t>82,36%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2686940</t>
+          <t>2682425</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2777003</t>
+          <t>2777371</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>79,51%</t>
+          <t>79,38%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>82,18%</t>
+          <t>82,19%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>5412903</t>
+          <t>5415771</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>5532151</t>
+          <t>5539076</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>81,33%</t>
+          <t>81,37%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>83,12%</t>
+          <t>83,22%</t>
         </is>
       </c>
     </row>
@@ -3712,12 +3712,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5818</t>
+          <t>5507</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>21016</t>
+          <t>19836</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3747,12 +3747,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>9854</t>
+          <t>9771</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>27230</t>
+          <t>25844</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3762,12 +3762,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3782,12 +3782,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>18367</t>
+          <t>18632</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>40123</t>
+          <t>40452</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3797,12 +3797,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,57%</t>
         </is>
       </c>
     </row>
@@ -3825,12 +3825,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>433130</t>
+          <t>434310</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>448328</t>
+          <t>448639</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3840,12 +3840,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,37%</t>
+          <t>95,63%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,72%</t>
+          <t>98,79%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3860,12 +3860,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>403000</t>
+          <t>404386</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>420376</t>
+          <t>420459</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3875,12 +3875,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,67%</t>
+          <t>93,99%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,71%</t>
+          <t>97,73%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>844253</t>
+          <t>843924</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>866009</t>
+          <t>865744</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3910,12 +3910,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,46%</t>
+          <t>95,43%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,92%</t>
+          <t>97,89%</t>
         </is>
       </c>
     </row>
@@ -4055,12 +4055,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>22019</t>
+          <t>22450</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>46468</t>
+          <t>45872</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>6,68%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4090,12 +4090,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>37073</t>
+          <t>36420</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>64797</t>
+          <t>65802</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>5,97%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,62%</t>
+          <t>10,78%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4125,12 +4125,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>64158</t>
+          <t>64322</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>101687</t>
+          <t>101417</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4140,12 +4140,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>7,82%</t>
         </is>
       </c>
     </row>
@@ -4168,12 +4168,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>640619</t>
+          <t>641215</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>665068</t>
+          <t>664637</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>93,24%</t>
+          <t>93,32%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,8%</t>
+          <t>96,73%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>545458</t>
+          <t>544453</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>573182</t>
+          <t>573835</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>89,38%</t>
+          <t>89,22%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>93,93%</t>
+          <t>94,03%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4238,12 +4238,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1195655</t>
+          <t>1195925</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1233184</t>
+          <t>1233020</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4253,12 +4253,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,16%</t>
+          <t>92,18%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,05%</t>
+          <t>95,04%</t>
         </is>
       </c>
     </row>
@@ -4398,12 +4398,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>30861</t>
+          <t>30986</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>55814</t>
+          <t>56823</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,19%</t>
+          <t>8,33%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>75682</t>
+          <t>74912</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>113938</t>
+          <t>112241</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10,67%</t>
+          <t>10,56%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>16,06%</t>
+          <t>15,82%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>113845</t>
+          <t>110923</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>158112</t>
+          <t>157749</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4483,12 +4483,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>7,97%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>11,36%</t>
+          <t>11,34%</t>
         </is>
       </c>
     </row>
@@ -4511,12 +4511,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>626049</t>
+          <t>625040</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>651002</t>
+          <t>650877</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>91,81%</t>
+          <t>91,67%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>95,47%</t>
+          <t>95,46%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4546,12 +4546,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>595636</t>
+          <t>597333</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>633892</t>
+          <t>634662</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>83,94%</t>
+          <t>84,18%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>89,33%</t>
+          <t>89,44%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4581,12 +4581,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1233325</t>
+          <t>1233688</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1277592</t>
+          <t>1280514</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>88,64%</t>
+          <t>88,66%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>91,82%</t>
+          <t>92,03%</t>
         </is>
       </c>
     </row>
@@ -4741,12 +4741,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>42655</t>
+          <t>41715</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>74981</t>
+          <t>71041</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4756,12 +4756,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>6,79%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>12,2%</t>
+          <t>11,56%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>88827</t>
+          <t>88245</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>129838</t>
+          <t>126836</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4791,12 +4791,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14,46%</t>
+          <t>14,37%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>21,14%</t>
+          <t>20,65%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>139543</t>
+          <t>139677</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>192361</t>
+          <t>188811</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4826,12 +4826,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>11,36%</t>
+          <t>11,37%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>15,65%</t>
+          <t>15,36%</t>
         </is>
       </c>
     </row>
@@ -4854,12 +4854,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>539636</t>
+          <t>543576</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>571962</t>
+          <t>572902</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4869,12 +4869,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>87,8%</t>
+          <t>88,44%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>93,06%</t>
+          <t>93,21%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>484426</t>
+          <t>487428</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>525437</t>
+          <t>526019</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4904,12 +4904,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>78,86%</t>
+          <t>79,35%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>85,54%</t>
+          <t>85,63%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1036519</t>
+          <t>1040069</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1089337</t>
+          <t>1089203</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4939,12 +4939,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>84,35%</t>
+          <t>84,64%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>88,64%</t>
+          <t>88,63%</t>
         </is>
       </c>
     </row>
@@ -5084,12 +5084,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>39651</t>
+          <t>40592</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>69158</t>
+          <t>67145</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5099,12 +5099,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>9,45%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>16,1%</t>
+          <t>15,64%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>97546</t>
+          <t>97505</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>138048</t>
+          <t>135678</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5134,12 +5134,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>21,78%</t>
+          <t>21,77%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>30,83%</t>
+          <t>30,3%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>148604</t>
+          <t>148049</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>195977</t>
+          <t>195707</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5169,12 +5169,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>16,94%</t>
+          <t>16,88%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>22,34%</t>
+          <t>22,31%</t>
         </is>
       </c>
     </row>
@@ -5197,12 +5197,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>360271</t>
+          <t>362284</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>389778</t>
+          <t>388837</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5212,12 +5212,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>83,9%</t>
+          <t>84,36%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>90,77%</t>
+          <t>90,55%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>309752</t>
+          <t>312122</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>350254</t>
+          <t>350295</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5247,12 +5247,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>69,17%</t>
+          <t>69,7%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>78,22%</t>
+          <t>78,23%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>681252</t>
+          <t>681522</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>728625</t>
+          <t>729180</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5282,12 +5282,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>77,66%</t>
+          <t>77,69%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>83,06%</t>
+          <t>83,12%</t>
         </is>
       </c>
     </row>
@@ -5427,12 +5427,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>44242</t>
+          <t>45711</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>73884</t>
+          <t>74212</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5442,12 +5442,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>14,28%</t>
+          <t>14,76%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>23,85%</t>
+          <t>23,96%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>95099</t>
+          <t>93530</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>128176</t>
+          <t>127728</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5477,12 +5477,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>26,86%</t>
+          <t>26,42%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>36,21%</t>
+          <t>36,08%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>148106</t>
+          <t>148860</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>193199</t>
+          <t>193521</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>22,31%</t>
+          <t>22,43%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>29,11%</t>
+          <t>29,15%</t>
         </is>
       </c>
     </row>
@@ -5540,12 +5540,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>235902</t>
+          <t>235574</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>265544</t>
+          <t>264075</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5555,12 +5555,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>76,15%</t>
+          <t>76,04%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>85,72%</t>
+          <t>85,24%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>225820</t>
+          <t>226268</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>258897</t>
+          <t>260466</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5590,12 +5590,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>63,79%</t>
+          <t>63,92%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>73,14%</t>
+          <t>73,58%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>470583</t>
+          <t>470261</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>515676</t>
+          <t>514922</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5625,12 +5625,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>70,89%</t>
+          <t>70,85%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>77,69%</t>
+          <t>77,57%</t>
         </is>
       </c>
     </row>
@@ -5770,12 +5770,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>42015</t>
+          <t>41287</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>70535</t>
+          <t>69546</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5785,12 +5785,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>16,82%</t>
+          <t>16,52%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>28,23%</t>
+          <t>27,84%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>132346</t>
+          <t>132286</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>173496</t>
+          <t>172162</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5820,12 +5820,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>34,02%</t>
+          <t>34,01%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>44,6%</t>
+          <t>44,26%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>182036</t>
+          <t>183806</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>232446</t>
+          <t>231262</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5855,12 +5855,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>28,5%</t>
+          <t>28,77%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>36,39%</t>
+          <t>36,2%</t>
         </is>
       </c>
     </row>
@@ -5883,12 +5883,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>179316</t>
+          <t>180305</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>207836</t>
+          <t>208564</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5898,12 +5898,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>71,77%</t>
+          <t>72,16%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>83,18%</t>
+          <t>83,48%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>215483</t>
+          <t>216817</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>256633</t>
+          <t>256693</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5933,12 +5933,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>55,4%</t>
+          <t>55,74%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>65,98%</t>
+          <t>65,99%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>406384</t>
+          <t>407568</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>456794</t>
+          <t>455024</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5968,12 +5968,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>63,61%</t>
+          <t>63,8%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>71,5%</t>
+          <t>71,23%</t>
         </is>
       </c>
     </row>
@@ -6113,12 +6113,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>278887</t>
+          <t>272492</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>345582</t>
+          <t>346774</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>7,95%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>10,08%</t>
+          <t>10,12%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>602211</t>
+          <t>599804</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>694407</t>
+          <t>695235</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>16,94%</t>
+          <t>16,87%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>19,53%</t>
+          <t>19,56%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>896548</t>
+          <t>895592</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1013551</t>
+          <t>1019284</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6198,12 +6198,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>12,84%</t>
+          <t>12,83%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>14,52%</t>
+          <t>14,6%</t>
         </is>
       </c>
     </row>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3081197</t>
+          <t>3080005</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3147892</t>
+          <t>3154287</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>89,92%</t>
+          <t>89,88%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>91,86%</t>
+          <t>92,05%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2860691</t>
+          <t>2859863</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2952887</t>
+          <t>2955294</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>80,47%</t>
+          <t>80,44%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>83,06%</t>
+          <t>83,13%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>5968326</t>
+          <t>5962593</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6085329</t>
+          <t>6086285</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6311,12 +6311,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>85,48%</t>
+          <t>85,4%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>87,16%</t>
+          <t>87,17%</t>
         </is>
       </c>
     </row>
@@ -6696,7 +6696,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7724</t>
+          <t>7713</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6726,12 +6726,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>5629</t>
+          <t>5706</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>18229</t>
+          <t>18581</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6741,12 +6741,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6761,12 +6761,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>7686</t>
+          <t>6968</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>21826</t>
+          <t>20315</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,49%</t>
         </is>
       </c>
     </row>
@@ -6804,7 +6804,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>411739</t>
+          <t>411750</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -6839,12 +6839,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>377526</t>
+          <t>377174</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>390126</t>
+          <t>390049</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6854,12 +6854,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,39%</t>
+          <t>95,3%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,58%</t>
+          <t>98,56%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6874,12 +6874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>793392</t>
+          <t>794903</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>807532</t>
+          <t>808250</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6889,12 +6889,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,32%</t>
+          <t>97,51%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,06%</t>
+          <t>99,15%</t>
         </is>
       </c>
     </row>
@@ -7034,12 +7034,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9435</t>
+          <t>9485</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>27962</t>
+          <t>27462</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7049,12 +7049,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7069,12 +7069,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>22130</t>
+          <t>22159</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>44233</t>
+          <t>44909</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7089,7 +7089,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,85%</t>
+          <t>7,97%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7104,12 +7104,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>36234</t>
+          <t>35752</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>64279</t>
+          <t>63466</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7119,12 +7119,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,5%</t>
         </is>
       </c>
     </row>
@@ -7147,12 +7147,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>562534</t>
+          <t>563034</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>581061</t>
+          <t>581011</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7162,12 +7162,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,26%</t>
+          <t>95,35%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,4%</t>
+          <t>98,39%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7182,12 +7182,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>519311</t>
+          <t>518635</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>541414</t>
+          <t>541385</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7197,7 +7197,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,15%</t>
+          <t>92,03%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -7217,12 +7217,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1089761</t>
+          <t>1090574</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1117806</t>
+          <t>1118288</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7232,12 +7232,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,43%</t>
+          <t>94,5%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,86%</t>
+          <t>96,9%</t>
         </is>
       </c>
     </row>
@@ -7377,12 +7377,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>34340</t>
+          <t>33274</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>61125</t>
+          <t>60294</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7392,12 +7392,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>9,14%</t>
+          <t>9,01%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7412,12 +7412,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>44306</t>
+          <t>44296</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>72945</t>
+          <t>73962</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7432,7 +7432,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>11,03%</t>
+          <t>11,18%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7447,12 +7447,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>84981</t>
+          <t>85753</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>125592</t>
+          <t>125651</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7462,7 +7462,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -7490,12 +7490,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>607972</t>
+          <t>608803</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>634757</t>
+          <t>635823</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7505,12 +7505,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>90,86%</t>
+          <t>90,99%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>94,87%</t>
+          <t>95,03%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7525,12 +7525,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>588441</t>
+          <t>587424</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>617080</t>
+          <t>617090</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7540,7 +7540,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>88,97%</t>
+          <t>88,82%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -7560,12 +7560,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1204891</t>
+          <t>1204832</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1245502</t>
+          <t>1244730</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7580,7 +7580,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>93,61%</t>
+          <t>93,55%</t>
         </is>
       </c>
     </row>
@@ -7720,12 +7720,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>46545</t>
+          <t>45668</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>76556</t>
+          <t>75247</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7735,12 +7735,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>7,07%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,85%</t>
+          <t>11,65%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7755,12 +7755,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>71011</t>
+          <t>70313</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>105199</t>
+          <t>104578</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7770,12 +7770,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,94%</t>
+          <t>10,83%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>16,21%</t>
+          <t>16,11%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7790,12 +7790,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>124050</t>
+          <t>122093</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>169840</t>
+          <t>170173</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7805,12 +7805,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,58%</t>
+          <t>9,43%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>13,11%</t>
+          <t>13,14%</t>
         </is>
       </c>
     </row>
@@ -7833,12 +7833,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>569492</t>
+          <t>570801</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>599503</t>
+          <t>600380</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>88,15%</t>
+          <t>88,35%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>92,8%</t>
+          <t>92,93%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7868,12 +7868,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>543878</t>
+          <t>544499</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>578066</t>
+          <t>578764</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7883,12 +7883,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>83,79%</t>
+          <t>83,89%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>89,06%</t>
+          <t>89,17%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7903,12 +7903,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1125285</t>
+          <t>1124952</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1171075</t>
+          <t>1173032</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7918,12 +7918,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>86,89%</t>
+          <t>86,86%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>90,42%</t>
+          <t>90,57%</t>
         </is>
       </c>
     </row>
@@ -8063,12 +8063,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>46421</t>
+          <t>45692</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>76942</t>
+          <t>77258</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8078,12 +8078,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>9,71%</t>
+          <t>9,56%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>16,1%</t>
+          <t>16,17%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8098,12 +8098,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>86303</t>
+          <t>86968</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>123113</t>
+          <t>124671</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8113,12 +8113,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>17,37%</t>
+          <t>17,5%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>24,78%</t>
+          <t>25,09%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>141894</t>
+          <t>140342</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>192205</t>
+          <t>189428</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8148,12 +8148,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>14,56%</t>
+          <t>14,4%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>19,72%</t>
+          <t>19,43%</t>
         </is>
       </c>
     </row>
@@ -8176,12 +8176,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>400976</t>
+          <t>400660</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>431497</t>
+          <t>432226</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8191,12 +8191,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>83,9%</t>
+          <t>83,83%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>90,29%</t>
+          <t>90,44%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8211,12 +8211,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>373736</t>
+          <t>372178</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>410546</t>
+          <t>409881</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8226,12 +8226,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>75,22%</t>
+          <t>74,91%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>82,63%</t>
+          <t>82,5%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8246,12 +8246,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>782562</t>
+          <t>785339</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>832873</t>
+          <t>834425</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8261,12 +8261,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>80,28%</t>
+          <t>80,57%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>85,44%</t>
+          <t>85,6%</t>
         </is>
       </c>
     </row>
@@ -8406,12 +8406,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>32311</t>
+          <t>33528</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>56743</t>
+          <t>58613</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8421,12 +8421,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>10,03%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>16,97%</t>
+          <t>17,53%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8441,12 +8441,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>65841</t>
+          <t>65761</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>98978</t>
+          <t>97175</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8456,12 +8456,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>17,43%</t>
+          <t>17,41%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>26,2%</t>
+          <t>25,72%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8476,12 +8476,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>105700</t>
+          <t>106494</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>147990</t>
+          <t>145401</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8491,12 +8491,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>14,84%</t>
+          <t>14,96%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>20,78%</t>
+          <t>20,42%</t>
         </is>
       </c>
     </row>
@@ -8519,12 +8519,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>277587</t>
+          <t>275717</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>302019</t>
+          <t>300802</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8534,12 +8534,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>83,03%</t>
+          <t>82,47%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>90,34%</t>
+          <t>89,97%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8554,12 +8554,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>278784</t>
+          <t>280587</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>311921</t>
+          <t>312001</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8569,12 +8569,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>73,8%</t>
+          <t>74,28%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>82,57%</t>
+          <t>82,59%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8589,12 +8589,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>564102</t>
+          <t>566691</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>606392</t>
+          <t>605598</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8604,12 +8604,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>79,22%</t>
+          <t>79,58%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>85,16%</t>
+          <t>85,04%</t>
         </is>
       </c>
     </row>
@@ -8749,12 +8749,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>39496</t>
+          <t>38903</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>62595</t>
+          <t>62900</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8764,12 +8764,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>15,37%</t>
+          <t>15,14%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>24,36%</t>
+          <t>24,47%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8784,12 +8784,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>102844</t>
+          <t>101782</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>143087</t>
+          <t>141805</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8799,12 +8799,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>25,7%</t>
+          <t>25,43%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>35,76%</t>
+          <t>35,44%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8819,12 +8819,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>146480</t>
+          <t>150087</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>197249</t>
+          <t>198648</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8834,12 +8834,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>22,29%</t>
+          <t>22,84%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>30,02%</t>
+          <t>30,23%</t>
         </is>
       </c>
     </row>
@@ -8862,12 +8862,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>194403</t>
+          <t>194098</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>217502</t>
+          <t>218095</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8877,12 +8877,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>75,64%</t>
+          <t>75,53%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>84,63%</t>
+          <t>84,86%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8897,12 +8897,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>257082</t>
+          <t>258364</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>297325</t>
+          <t>298387</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8912,12 +8912,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>64,24%</t>
+          <t>64,56%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>74,3%</t>
+          <t>74,57%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8932,12 +8932,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>459918</t>
+          <t>458519</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>510687</t>
+          <t>507080</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8947,12 +8947,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>69,98%</t>
+          <t>69,77%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>77,71%</t>
+          <t>77,16%</t>
         </is>
       </c>
     </row>
@@ -9092,12 +9092,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>246051</t>
+          <t>245974</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>310896</t>
+          <t>309842</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9112,7 +9112,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>9,16%</t>
+          <t>9,13%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9127,12 +9127,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>453078</t>
+          <t>451864</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>541806</t>
+          <t>539195</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9142,12 +9142,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>12,78%</t>
+          <t>12,75%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>15,29%</t>
+          <t>15,21%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9162,12 +9162,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>716938</t>
+          <t>721383</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>823410</t>
+          <t>829037</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9177,12 +9177,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>10,33%</t>
+          <t>10,4%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>11,87%</t>
+          <t>11,95%</t>
         </is>
       </c>
     </row>
@@ -9205,12 +9205,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3083454</t>
+          <t>3084508</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3148299</t>
+          <t>3148376</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9220,7 +9220,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>90,84%</t>
+          <t>90,87%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -9240,12 +9240,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3002736</t>
+          <t>3005347</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3091464</t>
+          <t>3092678</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9255,12 +9255,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>84,71%</t>
+          <t>84,79%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>87,22%</t>
+          <t>87,25%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9275,12 +9275,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6115482</t>
+          <t>6109855</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6221954</t>
+          <t>6217509</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9290,12 +9290,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>88,13%</t>
+          <t>88,05%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>89,67%</t>
+          <t>89,6%</t>
         </is>
       </c>
     </row>
@@ -9665,32 +9665,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>18393</t>
+          <t>20495</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5610</t>
+          <t>8627</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>43169</t>
+          <t>39951</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>10,79%</t>
+          <t>9,8%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9700,32 +9700,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>31375</t>
+          <t>34715</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>18933</t>
+          <t>19501</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>51760</t>
+          <t>54532</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>10,02%</t>
+          <t>9,58%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>16,53%</t>
+          <t>15,04%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9735,32 +9735,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>49768</t>
+          <t>55210</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>32060</t>
+          <t>36135</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>75007</t>
+          <t>81102</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>7,17%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,52%</t>
+          <t>10,53%</t>
         </is>
       </c>
     </row>
@@ -9778,32 +9778,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>381594</t>
+          <t>387298</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>356818</t>
+          <t>367842</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>394377</t>
+          <t>399166</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>95,4%</t>
+          <t>94,97%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>89,21%</t>
+          <t>90,2%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,6%</t>
+          <t>97,88%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9813,32 +9813,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>281825</t>
+          <t>327797</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>261440</t>
+          <t>307980</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>294267</t>
+          <t>343011</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>89,98%</t>
+          <t>90,42%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>83,47%</t>
+          <t>84,96%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>93,96%</t>
+          <t>94,62%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9848,32 +9848,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>663419</t>
+          <t>715095</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>638180</t>
+          <t>689203</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>681127</t>
+          <t>734170</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>93,02%</t>
+          <t>92,83%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>89,48%</t>
+          <t>89,47%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,5%</t>
+          <t>95,31%</t>
         </is>
       </c>
     </row>
@@ -9891,17 +9891,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -9926,17 +9926,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -9961,17 +9961,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -10008,32 +10008,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>29879</t>
+          <t>33415</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>19479</t>
+          <t>21184</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>46272</t>
+          <t>50809</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>7,04%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,98%</t>
+          <t>10,71%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -10043,32 +10043,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>51528</t>
+          <t>55399</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>32239</t>
+          <t>41060</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>70984</t>
+          <t>71629</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>11,06%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>8,19%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>13,88%</t>
+          <t>14,29%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10078,32 +10078,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>81407</t>
+          <t>88814</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>58556</t>
+          <t>70732</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>103404</t>
+          <t>111776</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>8,73%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>7,25%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>11,09%</t>
+          <t>11,46%</t>
         </is>
       </c>
     </row>
@@ -10121,32 +10121,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>391408</t>
+          <t>441042</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>375015</t>
+          <t>423648</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>401808</t>
+          <t>453273</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>92,91%</t>
+          <t>92,96%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>89,02%</t>
+          <t>89,29%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>95,38%</t>
+          <t>95,54%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -10156,32 +10156,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>459976</t>
+          <t>445684</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>440520</t>
+          <t>429454</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>479265</t>
+          <t>460023</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>89,93%</t>
+          <t>88,94%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>86,12%</t>
+          <t>85,71%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>93,7%</t>
+          <t>91,81%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -10191,32 +10191,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>851384</t>
+          <t>886726</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>829387</t>
+          <t>863764</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>874235</t>
+          <t>904808</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>91,27%</t>
+          <t>90,9%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>88,91%</t>
+          <t>88,54%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>93,72%</t>
+          <t>92,75%</t>
         </is>
       </c>
     </row>
@@ -10234,17 +10234,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>421287</t>
+          <t>474457</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>421287</t>
+          <t>474457</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>421287</t>
+          <t>474457</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -10269,17 +10269,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>511504</t>
+          <t>501083</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>511504</t>
+          <t>501083</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>511504</t>
+          <t>501083</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -10304,17 +10304,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>932791</t>
+          <t>975540</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>932791</t>
+          <t>975540</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>932791</t>
+          <t>975540</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -10351,32 +10351,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>57066</t>
+          <t>64289</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>42524</t>
+          <t>48308</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>72116</t>
+          <t>80093</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>10,66%</t>
+          <t>10,37%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>7,79%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>13,46%</t>
+          <t>12,92%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10386,32 +10386,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>112637</t>
+          <t>129436</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>98031</t>
+          <t>112742</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>128773</t>
+          <t>149089</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>20,79%</t>
+          <t>20,83%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>18,09%</t>
+          <t>18,14%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>23,77%</t>
+          <t>23,99%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10421,32 +10421,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>169703</t>
+          <t>193725</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>148960</t>
+          <t>169919</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>191783</t>
+          <t>220797</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>15,75%</t>
+          <t>15,6%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>13,83%</t>
+          <t>13,69%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>17,8%</t>
+          <t>17,79%</t>
         </is>
       </c>
     </row>
@@ -10464,32 +10464,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>478512</t>
+          <t>555656</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>463462</t>
+          <t>539852</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>493054</t>
+          <t>571637</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>89,34%</t>
+          <t>89,63%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>86,54%</t>
+          <t>87,08%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>92,06%</t>
+          <t>92,21%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10499,32 +10499,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>429162</t>
+          <t>492052</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>413026</t>
+          <t>472399</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>443768</t>
+          <t>508746</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>79,21%</t>
+          <t>79,17%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>76,23%</t>
+          <t>76,01%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>81,91%</t>
+          <t>81,86%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10534,32 +10534,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>907674</t>
+          <t>1047709</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>885594</t>
+          <t>1020637</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>928417</t>
+          <t>1071515</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>84,25%</t>
+          <t>84,4%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>82,2%</t>
+          <t>82,21%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>86,17%</t>
+          <t>86,31%</t>
         </is>
       </c>
     </row>
@@ -10577,17 +10577,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>535578</t>
+          <t>619945</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>535578</t>
+          <t>619945</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>535578</t>
+          <t>619945</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -10612,17 +10612,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>541799</t>
+          <t>621488</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>541799</t>
+          <t>621488</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>541799</t>
+          <t>621488</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -10647,17 +10647,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1077377</t>
+          <t>1241434</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1077377</t>
+          <t>1241434</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1077377</t>
+          <t>1241434</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -10694,32 +10694,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>132391</t>
+          <t>142109</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>55384</t>
+          <t>121038</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>192661</t>
+          <t>163179</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>14,93%</t>
+          <t>20,32%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>17,31%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>21,73%</t>
+          <t>23,33%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10729,32 +10729,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>193156</t>
+          <t>210594</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>164727</t>
+          <t>191897</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>215871</t>
+          <t>229205</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>27,13%</t>
+          <t>28,62%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>23,14%</t>
+          <t>26,08%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>30,33%</t>
+          <t>31,15%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10764,32 +10764,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>325546</t>
+          <t>352703</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>185568</t>
+          <t>323434</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>398713</t>
+          <t>381614</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>20,37%</t>
+          <t>24,57%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>11,61%</t>
+          <t>22,54%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>24,94%</t>
+          <t>26,59%</t>
         </is>
       </c>
     </row>
@@ -10807,32 +10807,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>754282</t>
+          <t>557324</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>694012</t>
+          <t>536254</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>831289</t>
+          <t>578395</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>85,07%</t>
+          <t>79,68%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>78,27%</t>
+          <t>76,67%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>93,75%</t>
+          <t>82,69%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10842,32 +10842,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>518697</t>
+          <t>525210</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>495982</t>
+          <t>506599</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>547126</t>
+          <t>543907</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>72,87%</t>
+          <t>71,38%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>69,67%</t>
+          <t>68,85%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>76,86%</t>
+          <t>73,92%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10877,32 +10877,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1272980</t>
+          <t>1082534</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1199813</t>
+          <t>1053623</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1412958</t>
+          <t>1111803</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>79,63%</t>
+          <t>75,43%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>75,06%</t>
+          <t>73,41%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>88,39%</t>
+          <t>77,46%</t>
         </is>
       </c>
     </row>
@@ -10920,17 +10920,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>886673</t>
+          <t>699433</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>886673</t>
+          <t>699433</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>886673</t>
+          <t>699433</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -10955,17 +10955,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>711853</t>
+          <t>735804</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>711853</t>
+          <t>735804</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>711853</t>
+          <t>735804</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -10990,17 +10990,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1598526</t>
+          <t>1435237</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1598526</t>
+          <t>1435237</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1598526</t>
+          <t>1435237</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -11037,32 +11037,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>153242</t>
+          <t>160917</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>136186</t>
+          <t>139599</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>174998</t>
+          <t>181506</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>27,35%</t>
+          <t>26,45%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>24,31%</t>
+          <t>22,95%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>31,24%</t>
+          <t>29,84%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11072,32 +11072,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>213669</t>
+          <t>238127</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>196351</t>
+          <t>220551</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>230938</t>
+          <t>257346</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>39,22%</t>
+          <t>39,25%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>36,05%</t>
+          <t>36,35%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>42,4%</t>
+          <t>42,41%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11107,32 +11107,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>366911</t>
+          <t>399044</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>337951</t>
+          <t>371255</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>391364</t>
+          <t>429042</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>33,21%</t>
+          <t>32,84%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>30,58%</t>
+          <t>30,55%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>35,42%</t>
+          <t>35,31%</t>
         </is>
       </c>
     </row>
@@ -11150,32 +11150,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>406995</t>
+          <t>447442</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>385239</t>
+          <t>426853</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>424051</t>
+          <t>468760</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>72,65%</t>
+          <t>73,55%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>68,76%</t>
+          <t>70,16%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>75,69%</t>
+          <t>77,05%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11185,32 +11185,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>331059</t>
+          <t>368638</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>313790</t>
+          <t>349419</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>348377</t>
+          <t>386214</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>60,78%</t>
+          <t>60,75%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>57,6%</t>
+          <t>57,59%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>63,95%</t>
+          <t>63,65%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11220,32 +11220,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>738053</t>
+          <t>816080</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>713600</t>
+          <t>786082</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>767013</t>
+          <t>843869</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>66,79%</t>
+          <t>67,16%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>64,58%</t>
+          <t>64,69%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>69,42%</t>
+          <t>69,45%</t>
         </is>
       </c>
     </row>
@@ -11263,17 +11263,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>560237</t>
+          <t>608359</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>560237</t>
+          <t>608359</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>560237</t>
+          <t>608359</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -11298,17 +11298,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>544728</t>
+          <t>606765</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>544728</t>
+          <t>606765</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>544728</t>
+          <t>606765</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -11333,17 +11333,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1104964</t>
+          <t>1215124</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1104964</t>
+          <t>1215124</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1104964</t>
+          <t>1215124</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -11380,32 +11380,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>99323</t>
+          <t>109620</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>84823</t>
+          <t>94422</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>112146</t>
+          <t>124757</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>27,03%</t>
+          <t>26,99%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>23,08%</t>
+          <t>23,24%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>30,52%</t>
+          <t>30,71%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11415,32 +11415,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>388406</t>
+          <t>205118</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>269997</t>
+          <t>190967</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>507415</t>
+          <t>221240</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>63,84%</t>
+          <t>46,71%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>44,38%</t>
+          <t>43,48%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>83,41%</t>
+          <t>50,38%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11450,32 +11450,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>487729</t>
+          <t>314738</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>350391</t>
+          <t>295061</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>712604</t>
+          <t>337484</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>49,98%</t>
+          <t>37,23%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>35,91%</t>
+          <t>34,9%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>73,03%</t>
+          <t>39,92%</t>
         </is>
       </c>
     </row>
@@ -11493,32 +11493,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>268124</t>
+          <t>296591</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>255301</t>
+          <t>281454</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>282624</t>
+          <t>311789</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>72,97%</t>
+          <t>73,01%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>69,48%</t>
+          <t>69,29%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>76,92%</t>
+          <t>76,76%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11528,32 +11528,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>219962</t>
+          <t>234048</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>100953</t>
+          <t>217926</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>338371</t>
+          <t>248199</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>36,16%</t>
+          <t>53,29%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>16,59%</t>
+          <t>49,62%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>55,62%</t>
+          <t>56,52%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11563,32 +11563,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>488085</t>
+          <t>530640</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>263210</t>
+          <t>507894</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>625423</t>
+          <t>550317</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>50,02%</t>
+          <t>62,77%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>26,97%</t>
+          <t>60,08%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>64,09%</t>
+          <t>65,1%</t>
         </is>
       </c>
     </row>
@@ -11606,17 +11606,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>367447</t>
+          <t>406211</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>367447</t>
+          <t>406211</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>367447</t>
+          <t>406211</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11641,17 +11641,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -11676,17 +11676,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>975814</t>
+          <t>845378</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>975814</t>
+          <t>845378</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>975814</t>
+          <t>845378</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -11723,32 +11723,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>111767</t>
+          <t>123432</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>99476</t>
+          <t>108456</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>123916</t>
+          <t>137418</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>39,53%</t>
+          <t>39,79%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>35,18%</t>
+          <t>34,96%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>43,82%</t>
+          <t>44,3%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11758,32 +11758,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>242893</t>
+          <t>268546</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>227957</t>
+          <t>252814</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>257456</t>
+          <t>283471</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>57,04%</t>
+          <t>57,8%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>53,53%</t>
+          <t>54,41%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>60,46%</t>
+          <t>61,01%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11793,32 +11793,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>354660</t>
+          <t>391977</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>335094</t>
+          <t>370478</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>373697</t>
+          <t>413309</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>50,05%</t>
+          <t>50,59%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>47,29%</t>
+          <t>47,82%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>52,74%</t>
+          <t>53,34%</t>
         </is>
       </c>
     </row>
@@ -11836,32 +11836,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>170992</t>
+          <t>186766</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>158843</t>
+          <t>172780</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>183283</t>
+          <t>201742</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>60,47%</t>
+          <t>60,21%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>56,18%</t>
+          <t>55,7%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>64,82%</t>
+          <t>65,04%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11871,32 +11871,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>182938</t>
+          <t>196063</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>168375</t>
+          <t>181138</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>197874</t>
+          <t>211795</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>42,96%</t>
+          <t>42,2%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>39,54%</t>
+          <t>38,99%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>46,47%</t>
+          <t>45,59%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -11906,32 +11906,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>353930</t>
+          <t>382830</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>334893</t>
+          <t>361498</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>373496</t>
+          <t>404329</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>49,95%</t>
+          <t>49,41%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>47,26%</t>
+          <t>46,66%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>52,71%</t>
+          <t>52,18%</t>
         </is>
       </c>
     </row>
@@ -11949,17 +11949,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -11984,17 +11984,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>425831</t>
+          <t>464609</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>425831</t>
+          <t>464609</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>425831</t>
+          <t>464609</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -12019,17 +12019,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>708590</t>
+          <t>774807</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>708590</t>
+          <t>774807</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>708590</t>
+          <t>774807</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -12066,32 +12066,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>602060</t>
+          <t>654276</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>465913</t>
+          <t>607107</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>668553</t>
+          <t>705157</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>17,43%</t>
+          <t>18,55%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>13,49%</t>
+          <t>17,22%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>19,36%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12101,32 +12101,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>1233663</t>
+          <t>1141936</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1069708</t>
+          <t>1093870</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1662016</t>
+          <t>1190892</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>33,73%</t>
+          <t>30,6%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>29,25%</t>
+          <t>29,32%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>45,44%</t>
+          <t>31,92%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12136,32 +12136,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>1835724</t>
+          <t>1796212</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1629138</t>
+          <t>1731327</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>2479075</t>
+          <t>1860958</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>25,81%</t>
+          <t>24,75%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>22,91%</t>
+          <t>23,85%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>34,86%</t>
+          <t>25,64%</t>
         </is>
       </c>
     </row>
@@ -12179,32 +12179,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>2851908</t>
+          <t>2872122</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2785415</t>
+          <t>2821241</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2988055</t>
+          <t>2919291</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>82,57%</t>
+          <t>81,45%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>80,64%</t>
+          <t>80,0%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>86,51%</t>
+          <t>82,78%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12214,32 +12214,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>2423619</t>
+          <t>2589492</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1995266</t>
+          <t>2540536</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2587574</t>
+          <t>2637558</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>66,27%</t>
+          <t>69,4%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>54,56%</t>
+          <t>68,08%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>70,75%</t>
+          <t>70,68%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12249,32 +12249,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>5275526</t>
+          <t>5461614</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>4632175</t>
+          <t>5396868</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>5482112</t>
+          <t>5526499</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>74,19%</t>
+          <t>75,25%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>65,14%</t>
+          <t>74,36%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>77,09%</t>
+          <t>76,15%</t>
         </is>
       </c>
     </row>
@@ -12292,17 +12292,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>3453968</t>
+          <t>3526398</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>3453968</t>
+          <t>3526398</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>3453968</t>
+          <t>3526398</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -12327,17 +12327,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>3657282</t>
+          <t>3731428</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>3657282</t>
+          <t>3731428</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>3657282</t>
+          <t>3731428</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -12362,17 +12362,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>7111250</t>
+          <t>7257826</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>7111250</t>
+          <t>7257826</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>7111250</t>
+          <t>7257826</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
